--- a/Debuggers/干员.xlsx
+++ b/Debuggers/干员.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\方舟杀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\ArkWars\Debuggers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A277EB-09DF-49D3-83C0-C4696CDDF21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAB3020-1470-4FFD-ADB1-CD0179412376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色" sheetId="1" r:id="rId1"/>
@@ -33,553 +33,526 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="306">
   <si>
     <t>阵营</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>血量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>塔拉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>死芒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>罗德岛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>焰影苇草</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>遥</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>炎</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>林</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>魔王</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>黑钢国际</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>涤火杰西卡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>莱茵生命</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>多萝西</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>雷缪安</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>拉特兰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>新约能天使</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>维多利亚</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>白铁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>谢拉格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>圣聆初雪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>卡西米尔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>瑕光</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>泥岩</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>薇薇安娜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>夕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>莱塔尼亚</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>纯烬艾雅法拉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>叙拉古</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>忍冬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>娜斯提</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>铃兰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>灵知</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>黑键</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>哥伦比亚</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>霍尔海雅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>山</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>乌萨斯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>怒潮寒冬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>早露</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>伊比利亚</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>海沫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>引星棘刺</t>
   </si>
   <si>
     <t>赫拉格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>雷姆必拓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>莱伊</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>珊比</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>逻各斯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>絮雨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>华法琳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>酒神</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>空弦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>寻澜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>东</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>斩业星熊</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>水月</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>汐斯塔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>黑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锡兰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>机动盾牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>投递坐标</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>共振装置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>白铁™多功能平台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>“小自在”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>本能的召唤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>迷狂牢笼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>屏障</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>阻挡下一次受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>护甲</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>在拥有护甲时受到伤害，优先扣取护甲，无法格挡真实伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>鼓舞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>悲叹的仆役</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>可置入召唤类、道具类装备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>可置入道具类装备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>宝具栏位X2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>道具栏位X2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>武器栏位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>可置入武器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>可置入防具</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>防具栏位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>真实伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无来源伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无视护甲</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>虚拟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>造成伤害，但无法获取伤害来源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>不可选中</t>
-  </si>
-  <si>
-    <t>隐藏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>迷彩</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>无敌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法受到伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>禁疗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法被指向性卡牌选中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法被指向性回复卡牌选中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缴械</t>
-  </si>
-  <si>
-    <t>沉默</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法使用技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>束缚</t>
-  </si>
-  <si>
-    <t>冻结</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>下一张卡牌无效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法使用或打出手牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法使用或打出手牌，无法使用技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法使用或打出伤害类卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法被指向性卡牌选中，使用卡牌或技能后失效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法被选中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>视为使用或打出</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>蓝毒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>萨米</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>提丰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>寒檀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>抵抗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>受到异常状态时进行一次判定，若结果为红色则抵消该状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>物理护甲</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>魔法护甲</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>在拥有护甲时受到魔法伤害，优先扣取护甲，无法格挡真实伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>在拥有护甲时受到物理伤害，优先扣取护甲，无法格挡真实伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>叙拉古</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>荒芜拉普兰德</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>缄默德克萨斯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能描述1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能描述2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能描述3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>衍生名称2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能名称1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能名称2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能名称3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>衍生描述1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>衍生描述2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>衍生名称1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>主动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锁定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>策略技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段开始时，你可以令本回合内你的所有指向类回复卡牌被视为【杀·物理】或【杀·法术】使用或打出，以此法使用的卡牌无次数限制且造成的伤害+1，若造成伤害则选择一名其他角色回复等量生命值。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>沉睡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>无法使用技能或打出卡牌，无法被指向性卡牌选中，受到伤害后失效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>限定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>觉醒技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>明灭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>光影迅捷剑</t>
@@ -587,117 +560,111 @@
   <si>
     <t>你的攻击范围始终为2。当场上有“灼燃损伤”触发时，你可以令其下一回合的出【杀】次数-1。
 修改：你的攻击范围始终为3。当场上有“灼燃损伤”触发时，你可以令其下一回合的出【杀】次数-1并对其造成1点真实伤害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以弃置1张红色【杀】，视为使用2张不计次数的【杀·灼燃】，若造成伤害则进行判定，判定结果为方片时获得“屏障”。
 修改：出牌阶段限一次，你可以弃置1张红色【杀】，视为使用3张不计次数的【杀·灼燃】，若造成伤害则进行判定，判定结果为红色时获得“屏障”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>灼燃损伤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>凋亡损伤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>侵蚀损伤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>神经损伤</t>
-  </si>
-  <si>
-    <t>狂躁损伤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其无法使用或打出伤害类卡牌，持续至其下回合结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其血量上限-2，持续至其下回合结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其非锁定技无效，持续至其下回合结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其受到的法术伤害+1，持续至其下回合结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其回合内出【杀】次数与造成伤害+1，持续至其下回合结束，其回合结束时失去2点血量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>庇护</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>令其下一次受到的伤害至多为1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得“屏障”。当场上有“屏障”触发时，你与其各摸1张牌。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，将投递坐标置入你的宝物栏。持有“投递坐标”的角色进入濒死状态时，你可以将“投递坐标”移出游戏并将对应角色的血量回复至其中“快递”数量。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以失去至多3个自己的“弹药”视为使用X张【杀·物理】，并获得X点护甲，该护甲持续至下个出牌阶段开始。（X为“弹药”失去数量）。弃牌阶段结束时，你可以弃置任意张【杀】并获得等量“弹药”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>使命必达！</t>
   </si>
   <si>
     <t>类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>功能卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>宝物卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>效果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>隐德来希</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>被动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你的手牌添加“共振”标记。每回合限一次，你获得当前角色弃置的第一张牌并添加“共振”标记，你可以将具有“共振”标记的卡牌可以作为“共振装置”使用。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>攻击范围2，出牌阶段限一次，你可以失去一点血量视为使用一张不计次数的【杀·法术】，以此法造成伤害时回复等量血量。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锁定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>被动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>过往尘埃</t>
@@ -707,61 +674,61 @@
 ①：对其造成1点法术伤害。
 ②：将该卡牌无效。
 ③：获取其一张牌并为卡牌添加“共振”标记。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>准备阶段，你可以摸一张牌并选择其中一个策略触发：
 ①：本回合攻击范围+1且你使用的【杀】伤害+1
 ②：可以额外使用一张【杀】且【杀】可以额外指定一名目标</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你能指定拥有“沉睡”的角色为目标。每回合限一次，当有角色失去“沉睡”时，你从牌堆中抽取一张指向类回复卡牌。你可以弃置2张手牌令一名其他角色获得“沉睡”。若该角色已经拥有“沉睡”，则对其造成1点法术伤害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以失去至多3个自己的“弹药”，并选择X个攻击范围内的角色对其造成1点物理伤害。（X为“弹药”失去数量）当你造成伤害时，你可以失去1个自己的“弹药”令此次伤害+1。弃牌阶段结束时，你可以弃置任意张【杀】并获得等量“弹药”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可将一张手牌移出游戏并扣置于【投递坐标】下，称为“快递”，若如此做，你可将宝物栏里的【投递坐标】置入一名其他角色的宝物栏；你能将“快递”如手牌般使用或打出。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>血镰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>炼金单元</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>沙地兽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>武器卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以弃置2张手牌并选择一名角色，令其获得“屏障”，以此法获得的“屏障”失效后，其回复1点血量并获得“庇护”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你对其他干员造成伤害时，可以摸1张牌并将1张手牌置于其干员牌上称之为“心烛”。拥有“心烛”的干员受到伤害时，你摸一张牌，其死亡时，你收回“心烛”并增加一点体力上限。你的【杀】可以指定任意名拥有“心烛”的干员作为目标。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得2个“弹药”，令场上所有其他拉特兰干员获得2个“弹药”。当你失去“弹药”后摸1张牌。所有拉特兰干员攻击范围内的目标视为在你的攻击范围内。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始或回合开始时，若“血镰”不在场上，则你可以失去一点血量将“血镰”置入你的武器栏，若“血镰”在场上，则你可以移动“血镰”。当“血镰”持有者血量产生变化时，你摸1张牌。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得“屏障”，当你失去屏障时，回复1点血量并摸1张牌。每回合结束时，若你本回合没有受到伤害，则你可以弃置2张手牌获得“屏障”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>灼痕</t>
@@ -771,7 +738,7 @@
   </si>
   <si>
     <t>每个回合结束时，若本居游戏场上累计有两次“灼燃损伤”触发，你摸2张牌并回复1点体力，然后修改“明灭”和“光影迅捷剑”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以弃置一张对应花色的手牌（每个花色限一次）永久升级所有【白铁™多功能平台】。
@@ -779,7 +746,7 @@
 ②梅花：每回合首次受到伤害后摸2张牌。
 ③方片：每回合首次造成的伤害+1。
 ④红桃：出牌阶段开始时回复1点血量。）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>圣山的祝福</t>
@@ -789,58 +756,58 @@
   </si>
   <si>
     <t>出牌阶段，对你自己使用，抽取三张卡牌，弃置其中一张。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段，选择一名角色，令其抽取两张卡牌，弃置其中一张。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段，你可以将两张相同颜色的手牌当作“圣山的祝福”使用，两张不同颜色的手牌当作“霜涛覆岭”使用。（每种花色组合每回合限一次）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以弃置X张牌并失去“屏障”，然后令攻击范围内的X名角色获得“晕眩”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>隐狐之艺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段，你可以选择其中一个策略触发并移除：
 ①：你可以令一名攻击范围内的角色获得“沉默”并视为对其使用1张不计次数的【杀·法术】。
 ②：你可以令一名攻击范围内的角色在本回合内受到的法术伤害+1，并视为对其使用1张不计次数的【杀·法术】。
 ③：你可以令X名攻击范围内的角色获得“晕眩”，并视为对其中任意数量目标使用至多2张不计次数的【杀·法术】。（X为你的攻击范围）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，将【机动盾牌】置入你的宝物区。回合开始时，你可以弃置2张手牌将【机动盾牌】置入你的宝物区，若你的宝物区有【机动盾牌】，则获得1点护甲。当你的护甲减少时，抽一张牌。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锁定技：回合开始时，获得1点护甲。出牌阶段，你可以移除全部护甲并对一名攻击范围内的角色造成等量伤害，随后销毁机动盾牌。此宝物离开宝物区时销毁。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>被动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>每回合限一次，当你使用或打出一张牌后，可以摸一张牌展示并交给场上任意一名角色，若展示牌与使用牌类型相同，此技能视为未发动过。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>主动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>兰登战术</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>武器卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -856,103 +823,103 @@
       </rPr>
       <t>5，你的杀可以额外指定一名角色。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锁定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段，你令下一张指向性卡牌额外选择至多两个目标，该卡牌造成伤害时令对应目标获得“晕眩”，在该卡牌结算后你流失X点体力。（X为该卡牌选择目标数减去造成伤害数）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>浮空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>自身与其他角色相互间距离均+2，持续至其下回合结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得2个“弹药”，每当场上“弹药”数量减少时，你进行一次判定，判定结果为黑桃时，你选择对失去“弹药”角色攻击范围内的一名其他角色造成1点物理伤害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你对血量小于已损失血量的角色造成伤害时，令其获得“浮空”。所有拥有“浮空”的角色视为在你的攻击范围内。当你对拥有“浮空”的角色造成伤害时，令其获得“沉默”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>6/6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>8/8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你受到伤害后，你摸1张牌并将1张手牌置于干员牌上称为“我执”，随后你可以视为对伤害来源使用一张“我执”中的牌。你的手牌上限额外增加X（X为“我执”的数量），你的血量不大于“我执”时，你无法被指向类回复卡牌指定。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你获得任意张“我执”并使用，以此法造成伤害的卡牌令你回复1点血量，回合结束时，你失去X点血量。（X为获得“我执”的数量减去造成伤害数）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>7/7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你对攻击范围内血量小于已损伤血量的角色造成伤害+1且在对其造成伤害后回复1点血量。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当一名角色获得“浮空”后，你可以对其造成X点伤害并摸X张牌。（X为你与其距离-1且至多为3。）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得屏障，当你的“屏障”触发时，你摸1张牌。每回合限一次，一名角色使用【杀】造成伤害后，你可以弃置一张手牌视为使用【杀·物理】，若你本次使用的【杀·物理】造成伤害，则你获得“屏障”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>准备阶段，将【兰登战术】置入你的武器栏。出牌阶段限一次，你可以弃置至多X张【杀】视为使用X张不计入次数的【杀·物理】，以此法转化的【杀·物理】造成伤害后，你摸1张牌。（X为你的血量除以2向上取整）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你造成血量回复时摸1张牌，若目标角色拥有负面标记则随机移除1个并摸1张牌。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你展示一名其他角色的一张手牌并获得，若为红色，则令该角色回复1点血量且此技能视为未发动过，若为黑色，则你令其下次受到伤害后摸2张牌。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你将3个【白铁™多功能平台】置入场上角色的宝物栏。（每名角色至多获得一个【白铁™多功能平台】）当【白铁™多功能平台】销毁时，你摸X张牌。（X为【白铁™多功能平台】升级次数）回合开始时，你可以弃置3张手牌将【白铁™多功能平台】置入一名角色的宝物栏。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你的手牌上限+2。此宝物离开宝物区时销毁。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你进入濒死状态时，你可以移除场上所有的“寒冷”标记令你与伤害来源获得“冻结”，然后减少2点血量上限并血量回复至X并摸X张牌。（X为移除的“寒冷”标记数量且至多为5。）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你每回合使用的前2张卡牌可以额外指定一个目标，回合结束时，你对所有拥有“冻结”的角色造成1点法术伤害并移除“冻结”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>你失去“迷彩”后摸2张牌且下一张使用的牌无法被响应。当你令一名其他角色进入濒死状态时，获得“迷彩”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你使用伤害类卡牌指向一名角色结算后，你摸1张牌并展示。若展示牌为红色，则你获得“迷彩”，若展示牌为黑色，则你视为使用一张【杀·物理】（该【杀】无法触发“隐狐之艺”）。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>游戏开始时，你获得“屏障”。当你失去屏障时，你可以视为对攻击范围内任意名角色使用一张【杀】。回合开始或回合结束时，若你没有“屏障”，则可以弃置2张手牌获得“屏障”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -968,19 +935,19 @@
       </rPr>
       <t>/8</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>8/8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>策略技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当前回合结束时，若你的血量与手牌数均未发生变动，则你可以摸X张牌并将手牌中的X张牌以任意顺序放回牌堆顶。（X为你的体力上限）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -998,23 +965,23 @@
       <t>5，每个回合结束时，若本回合你没有受到伤害，则回复1点血量，你的出杀数量与造成的伤害+1。
 ②：将血量上限调整为7，你使用【杀】结算后视为额外使用一张相同的卡牌（该虚拟【杀】无法触发本技能），你的攻击范围+1，你的【杀】可以额外指定至多2名角色。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>7/7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锁定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>旧日残影</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>功能卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1030,7 +997,7 @@
       </rPr>
       <t>1点法术伤害。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1046,7 +1013,7 @@
       </rPr>
       <t>/6</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1062,7 +1029,7 @@
       </rPr>
       <t>/5</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1078,11 +1045,11 @@
       </rPr>
       <t>/7</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>有角色造成法术伤害时，你可以摸一张牌并将一张手牌置于干员牌上称为“骰子”。你的“骰子”减少时下一次造成的伤害附加等量“凋亡损伤”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1102,28 +1069,28 @@
 ③：对当前场上血量最高的一名其他角色造成X点伤害。
 （X为本回合该技能发动次数+1）</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>前方施工</t>
   </si>
   <si>
     <t>6/6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>宝物卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>前方施工·修改①：“拱卫”
 前方施工·修改②：“执行”
 前方施工·修改③：栖脚地</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1141,7 +1108,7 @@
 ②：你可以将“监工专员”置入一名角色的宝物栏，令“监工专员”持有者摸2张牌。场上至多存在3个“监工专员”。
 ③：将“应急承重小组”置入一名角色的宝物栏，若场上已有“应急承重小组”则将其升级，在“应急承重小组”销毁后你摸等量张牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1160,13 +1127,13 @@
 ②：将“监工专员”置入一名角色的宝物栏，令“监工专员”持有者摸2张牌并获得“屏障”。
 ③：将“应急承重小组”置入一名角色的宝物栏，若场上已有“应急承重小组”则将其升级，在“应急承重小组”销毁后你摸等量张牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>①：“质检专员”
 ②：“监工专员”
 ③：“应急承重小组”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1182,11 +1149,11 @@
       </rPr>
       <t>时，你修改“过往尘埃”。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你令下一张使用的卡牌指定攻击范围内的所有角色且不可响应，若该卡牌造成伤害，则令目标获得“眩晕”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1203,7 +1170,7 @@
       <t>张牌并可以对伤害来源使用使用一张手牌，随后失去一个“微尘”。（X为其拥有“微尘”数量且至多为3）
 修改：游戏开始时你获得3个“微尘”。每回合限一次，拥有“微尘”的角色受到伤害时，其摸X张牌并可以展示一张手牌视为对伤害来源使用，随后失去一个“微尘”。（X为其拥有“微尘”数量且至多为3，每张手牌每回合限一次）</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1221,31 +1188,31 @@
 ②：回合开始时，你可以弃置2张手牌获得“屏障”。场上至多存在3个“质检专员”。该卡牌离开宝物栏时销毁。
 ③：回合开始时你弃置攻击范围内至多X名角色X张牌，摸牌阶段你额外摸X张牌，你的血量上限+X（当“应急承重小组”离开你的宝物栏时失去以此法获得的生命上限）。（X为“应急承重小组”被升级的次数+1）该卡牌离开宝物栏时销毁。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>被动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>主动技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>回合开始时，你将“沙地兽”置于一名角色的宝物栏，拥有“沙地兽”的角色及其相邻角色视为在你的攻击范围内，当你对拥有“沙地兽”角色攻击范围内的角色造成伤害时，你摸2张牌并弃置其中的任意张牌获得等量“子弹”（你至多获得8个子弹）。当你使用【杀】时，你可以消耗1个“子弹”令此杀不计次数。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你消耗全部“子弹”并从牌堆中获取等量张【杀】依次对攻击范围内的一名角色使用，若你令其进入濒死则将你的“子弹”补充至体力上限。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>矢量传送带</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>标记</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1261,7 +1228,7 @@
       </rPr>
       <t>1张牌且此技能视为未发动过。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1277,11 +1244,11 @@
       </rPr>
       <t>1的角色时令其获得“侵蚀”，当你令一名角色获得“侵蚀损伤”时，获得1“护甲”并摸1张牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>限定技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1301,15 +1268,15 @@
 ③功能牌：令其中一个目标获得X个“凋亡”。
 （X为该技能本回合触发次数且至多为3）</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>不稳定血浆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>基本卡牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1325,7 +1292,7 @@
       </rPr>
       <t>1点血量，令本回合你下一次造成的伤害翻倍。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1341,11 +1308,11 @@
       </rPr>
       <t>1点血量令本次伤害翻倍。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>永恒狩猎</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1361,14 +1328,14 @@
       </rPr>
       <t>1张牌。你对血量小于已损失血量角色造成的回复数值+1。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>冰原秩序</t>
   </si>
   <si>
     <t>选择一名角色，直到其死亡前你仅可选择自身与其为目标，你对其使用的卡牌无次数距离限制，当你使用卡牌指定该角色时，你可以弃置一张手牌视为使用该卡牌（无法触发永恒狩猎），若目标死亡则该技能视为未发动过并修改“冰原秩序”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1385,19 +1352,19 @@
       </rPr>
       <t>1张手牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你造成伤害时，你摸一张牌后弃置一张手牌并令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你造成伤害时，你令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。你无法获得“冻结”且对“冻结”角色造成的伤害+1。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>冰焰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1413,43 +1380,43 @@
       </rPr>
       <t>1张手牌并进行三次判定，当判定结果为黑色时获得“寒冷”。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段，对所有角色使用。目标角色需要依次打出一张【闪】，否则该角色受到一点法术伤害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>提喻</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>延异视阈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>直到你的下个回合开始，将你的攻击范围调整为3，在此期间使用指向类卡牌可以选择攻击范围内的所有角色且无次数限制，同时令攻击范围内所有角色的指向类卡牌延迟X回合结算（X为其与你的距离），若你的下回合开始时仍有未结算的卡牌，你中止其结算并获得，你可以将以此法获得的卡牌当作不计次数的【杀·凋亡】使用。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当“死芒”使用手牌指定唯一目标时，你可以弃置一张牌视为使用同名牌指定相同目标。出牌阶段，你可交给“死芒”一张牌销毁【悲叹的仆役】。该卡牌离开宝物栏时销毁。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>觉醒技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>群体性谵妄</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>形为心役</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>堕梦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1465,7 +1432,7 @@
       </rPr>
       <t>1点血量上限并将手牌数补充至血量上限，随后修改“群体性谵妄”。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1481,7 +1448,7 @@
       </rPr>
       <t>1张牌，并视为对其使用1张【杀·神经】。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1508,7 +1475,7 @@
       <t xml:space="preserve">
 修改：一名角色回合结束时，若有角色在本回合内造成或受到伤害，则你可以将一张非基本牌视为“本能的召唤”对其中一名角色使用。当有角色获得“神经损伤”时，你可以将“迷狂牢笼”置入其宝物栏。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1524,27 +1491,27 @@
       </rPr>
       <t>1张手牌卡牌销毁“迷狂牢笼”。该卡牌离开宝物栏时销毁。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>噩愿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>冠死以冕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>回光黯淡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>蓝莓与黑巧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>破斩桎梏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1560,7 +1527,7 @@
       </rPr>
       <t>1张牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1576,16 +1543,16 @@
       </rPr>
       <t>6张，则你失去1点血量上限并修改“冠死以冕”。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>每轮每名角色限一次，你可以观看一位拥有【悲叹的仆役】角色的手牌并选择其中一张使用或打出。（以此法使用的牌无次数限制且目标由你指定）
 修改：每轮每名角色限两次，你可以观看一位拥有【悲叹的仆役】角色的手牌并选择其中一张使用或打出。（以此法使用的牌无次数限制且目标由你指定）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当你杀死一名角色时，你获得其所有卡牌并将“蓝莓与黑巧”重置为游戏开始时的状态。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1601,7 +1568,7 @@
       </rPr>
       <t>2张牌。你无法获得“冻结”。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1617,7 +1584,7 @@
       </rPr>
       <t>1张功能卡牌。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1633,28 +1600,79 @@
       </rPr>
       <t>1张杀，若有角色拒绝，则你对其造成1点法术伤害。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>当前回合结束时，若你本回合触发过“灼痕”，则你可以选择至多两名角色，令其各视为使用一张【杀·法术】，若该【杀·法术】令一名角色进入濒死，则你视为使用一张【杀·法术】。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>每回合限一次，当有卡牌进入弃牌堆时，你摸一张与其类型相同的卡牌，以此法获得的非装备卡牌使用不计次数且可以额外指定一个目标。当你造成伤害后，你可以令目标下一次受到的法术伤害+1，若该伤害为法术伤害，则你可以选择一名角色回复等量血量。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可选中</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无敌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁疗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缴械</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉默</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>束缚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻结</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>神经损伤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂躁损伤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="思源黑体 CN Bold"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1767,28 +1785,40 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1796,97 +1826,85 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2208,47 +2226,47 @@
         <v>2</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F1" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="K1" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="L1" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>129</v>
-      </c>
       <c r="N1" s="20" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P1" s="31" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="10"/>
       <c r="R1" s="10" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="S1" s="31"/>
       <c r="T1" s="10"/>
@@ -2268,21 +2286,21 @@
         <v>7</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D2" s="31"/>
       <c r="E2" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="J2" s="31"/>
       <c r="K2" s="23"/>
@@ -2301,21 +2319,21 @@
         <v>55</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="20" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G3" s="31"/>
       <c r="H3" s="20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="J3" s="31"/>
       <c r="K3" s="20"/>
@@ -2334,21 +2352,21 @@
         <v>56</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>205</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>216</v>
       </c>
       <c r="G4" s="31"/>
       <c r="H4" s="20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="J4" s="31"/>
       <c r="K4" s="20"/>
@@ -2367,21 +2385,21 @@
         <v>36</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="20" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="20" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="J5" s="31"/>
       <c r="K5" s="20"/>
@@ -2400,14 +2418,14 @@
         <v>37</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="20" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G6" s="31"/>
       <c r="H6" s="20"/>
@@ -2429,21 +2447,21 @@
         <v>12</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="20" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="J7" s="31"/>
       <c r="K7" s="20"/>
@@ -2452,10 +2470,10 @@
         <v>60</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="P7" s="26"/>
       <c r="R7" s="14"/>
@@ -2468,21 +2486,21 @@
         <v>53</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="20" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G8" s="31"/>
       <c r="H8" s="20" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="J8" s="31"/>
       <c r="K8" s="20"/>
@@ -2501,21 +2519,21 @@
         <v>23</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="23" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J9" s="31"/>
       <c r="K9" s="28"/>
@@ -2534,32 +2552,32 @@
         <v>25</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="20" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="M10" s="31"/>
       <c r="N10" s="20"/>
@@ -2575,21 +2593,21 @@
         <v>15</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="J11" s="31"/>
       <c r="K11" s="20"/>
@@ -2608,30 +2626,30 @@
         <v>17</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="M12" s="31"/>
       <c r="N12" s="20"/>
@@ -2647,21 +2665,21 @@
         <v>52</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="20"/>
@@ -2680,21 +2698,21 @@
         <v>28</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="20"/>
@@ -2713,21 +2731,21 @@
         <v>34</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="20" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="20" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="J15" s="31"/>
       <c r="K15" s="20"/>
@@ -2746,21 +2764,21 @@
         <v>14</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="20" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="J16" s="31"/>
       <c r="K16" s="20"/>
@@ -2779,16 +2797,16 @@
         <v>31</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="G17" s="31"/>
       <c r="H17" s="20"/>
@@ -2797,22 +2815,22 @@
       <c r="K17" s="20"/>
       <c r="L17" s="22"/>
       <c r="M17" s="31" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="O17" s="32" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="P17" s="31" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="R17" s="37" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -2823,27 +2841,27 @@
         <v>46</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="20" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="20" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I18" s="32" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="J18" s="31"/>
       <c r="K18" s="20"/>
       <c r="L18" s="22"/>
       <c r="M18" s="31" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="N18" s="20"/>
       <c r="O18" s="25"/>
@@ -2858,30 +2876,30 @@
         <v>47</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="20" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="20" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I19" s="32" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="J19" s="31"/>
       <c r="K19" s="20"/>
       <c r="L19" s="22"/>
       <c r="M19" s="31" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="O19" s="36"/>
       <c r="P19" s="26"/>
@@ -2892,36 +2910,36 @@
         <v>5</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="23" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G20" s="31"/>
       <c r="H20" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="J20" s="31"/>
       <c r="K20" s="20"/>
       <c r="L20" s="29"/>
       <c r="M20" s="31" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="N20" s="20" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="P20" s="26"/>
       <c r="R20" s="14"/>
@@ -2934,23 +2952,23 @@
         <v>10</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G21" s="31"/>
       <c r="H21" s="20" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I21" s="38" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="J21" s="31"/>
       <c r="K21" s="20"/>
@@ -2969,21 +2987,21 @@
         <v>24</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="23" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G22" s="31"/>
       <c r="H22" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="J22" s="31"/>
       <c r="K22" s="20"/>
@@ -3002,25 +3020,25 @@
         <v>48</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="J23" s="31"/>
       <c r="K23" s="20"/>
@@ -3039,23 +3057,23 @@
         <v>50</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="20" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="J24" s="31"/>
       <c r="K24" s="20"/>
@@ -3068,31 +3086,31 @@
     </row>
     <row r="25" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C25" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>256</v>
-      </c>
       <c r="F25" s="32" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="J25" s="31"/>
       <c r="K25" s="20"/>
@@ -3105,27 +3123,27 @@
     </row>
     <row r="26" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="G26" s="40"/>
       <c r="H26" s="20" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I26" s="32" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="J26" s="31"/>
       <c r="K26" s="20"/>
@@ -3144,43 +3162,43 @@
         <v>4</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="J27" s="31" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="L27" s="32" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="M27" s="31" t="s">
         <v>72</v>
       </c>
       <c r="N27" s="20" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="O27" s="22" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="P27" s="26"/>
       <c r="R27" s="14"/>
@@ -3193,25 +3211,25 @@
         <v>6</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="J28" s="27"/>
       <c r="K28" s="20"/>
@@ -3230,21 +3248,21 @@
         <v>19</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D29" s="31"/>
       <c r="E29" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G29" s="27"/>
       <c r="H29" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="J29" s="31"/>
       <c r="K29" s="20"/>
@@ -3253,10 +3271,10 @@
         <v>63</v>
       </c>
       <c r="N29" s="20" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="P29" s="26"/>
       <c r="R29" s="14"/>
@@ -3269,52 +3287,52 @@
         <v>51</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I30" s="32" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="K30" s="39" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="L30" s="32" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M30" s="31" t="s">
         <v>65</v>
       </c>
       <c r="N30" s="20" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="O30" s="36" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="P30" s="31" t="s">
         <v>66</v>
       </c>
       <c r="Q30" s="20" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="R30" s="35" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3444,24 +3462,24 @@
       </c>
       <c r="D36" s="31"/>
       <c r="E36" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G36" s="31"/>
       <c r="H36" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="J36" s="31"/>
       <c r="K36" s="20" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="M36" s="31"/>
       <c r="N36" s="20"/>
@@ -3481,17 +3499,17 @@
       </c>
       <c r="D37" s="31"/>
       <c r="E37" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="J37" s="31"/>
       <c r="K37" s="20"/>
@@ -3514,19 +3532,19 @@
       </c>
       <c r="D38" s="31"/>
       <c r="E38" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="J38" s="31"/>
       <c r="K38" s="20"/>
@@ -3562,31 +3580,31 @@
     </row>
     <row r="40" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="31" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C40" s="21">
         <v>7</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="J40" s="31"/>
       <c r="K40" s="20"/>
@@ -3599,10 +3617,10 @@
     </row>
     <row r="41" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="31" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="31"/>
@@ -3632,17 +3650,17 @@
       </c>
       <c r="D42" s="31"/>
       <c r="E42" s="20" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G42" s="31"/>
       <c r="H42" s="20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="J42" s="31"/>
       <c r="K42" s="20"/>
@@ -3719,7 +3737,7 @@
       <c r="K45" s="20"/>
       <c r="L45" s="22"/>
       <c r="M45" s="31" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="N45" s="20"/>
       <c r="O45" s="25"/>
@@ -3754,7 +3772,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="31"/>
@@ -3777,7 +3795,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA47">
     <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3789,8 +3807,8 @@
   <sheetFormatPr defaultRowHeight="88.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.375" style="14" customWidth="1"/>
-    <col min="3" max="3" width="43" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="14" customWidth="1"/>
+    <col min="3" max="3" width="46.625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3798,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3809,10 +3827,10 @@
         <v>62</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3820,80 +3838,80 @@
         <v>61</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3901,260 +3919,260 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89AE271D-F804-4172-BED6-166B12FB38A3}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.625" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="21.625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="113.375" style="20" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="20" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" t="s">
-        <v>116</v>
+      <c r="A3" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
+      <c r="A4" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="31" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="20" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="20" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B11" t="s">
-        <v>106</v>
+      <c r="B11" s="20" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B16" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" t="s">
-        <v>112</v>
-      </c>
-    </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B33" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="31" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B33" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>145</v>
-      </c>
-      <c r="B34" t="s">
-        <v>149</v>
+      <c r="B34" s="20" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>147</v>
-      </c>
-      <c r="B36" t="s">
-        <v>152</v>
+      <c r="A35" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="49.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="A47" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="A48" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="20" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="A50" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="20" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Debuggers/干员.xlsx
+++ b/Debuggers/干员.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\ArkWars\Debuggers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAB3020-1470-4FFD-ADB1-CD0179412376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC82070-5CB0-408F-84FE-0EAB306C064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色" sheetId="1" r:id="rId1"/>
@@ -3918,7 +3918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89AE271D-F804-4172-BED6-166B12FB38A3}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.625" style="31" customWidth="1"/>
@@ -4131,7 +4131,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="49.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="31" t="s">
         <v>305</v>
       </c>
@@ -4139,35 +4139,35 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="31" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B43" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="31" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B44" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="31" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B45" s="20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="31" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B46" s="20" t="s">
         <v>79</v>
       </c>
     </row>
